--- a/practice/data/theory/jungol/01_초등(미완)/정올-문제목차.xlsx
+++ b/practice/data/theory/jungol/01_초등(미완)/정올-문제목차.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DCT2\Desktop\DCT2_공유폴더\StepCode\practice\data\theory\jungol\01_초등(미완)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\DCT2\Desktop\DCT2_공유폴더\StepCode\practice\data\theory\jungol\01_초등(미완)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B82078-9ADA-4F62-8B2F-25A446512182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{66877C7C-360F-440C-8F87-E7237B9EE784}"/>
+    <workbookView xWindow="-94" yWindow="-94" windowWidth="28997" windowHeight="15677"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
   <si>
     <t>정올 초등부</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -230,12 +229,91 @@
     <t>* 2026년도에 새로 추가할 문제</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>2019년도 6번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년도 7번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년도 9번</t>
+  </si>
+  <si>
+    <t>2020년도 7번</t>
+  </si>
+  <si>
+    <t>2020년도 8번</t>
+  </si>
+  <si>
+    <t>2020년도 9번</t>
+  </si>
+  <si>
+    <t>2021년도 7번</t>
+  </si>
+  <si>
+    <t>2021년도 9번</t>
+  </si>
+  <si>
+    <t>2022년도 8번</t>
+  </si>
+  <si>
+    <t>2022년도 9번</t>
+  </si>
+  <si>
+    <t>2025년도 11번</t>
+  </si>
+  <si>
+    <t>2020년도 11번</t>
+  </si>
+  <si>
+    <t>2020년도 10번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년도 3번</t>
+  </si>
+  <si>
+    <t>2019년도 2번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년도 8번</t>
+  </si>
+  <si>
+    <t>2019년도 3번</t>
+  </si>
+  <si>
+    <t>2019년도 5번</t>
+  </si>
+  <si>
+    <t>2021년도 1번</t>
+  </si>
+  <si>
+    <t>2021년도 8번</t>
+  </si>
+  <si>
+    <t>2021년도 11번</t>
+  </si>
+  <si>
+    <t>나머지 만들기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>통로 위의 강아지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +349,22 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -331,7 +425,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -344,14 +438,20 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -668,121 +768,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BD1FCD0-E876-4C86-BFDD-4928ED764E73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:U62"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="11.5625" customWidth="1"/>
-    <col min="3" max="3" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="18.125" customWidth="1"/>
-    <col min="7" max="7" width="12.5625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" customWidth="1"/>
     <col min="8" max="9" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21" ht="24.75" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:21" ht="23.6" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:21" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="M3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:21" ht="16.95" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="6"/>
       <c r="E4" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="M4" s="6" t="s">
+      <c r="I4" s="6"/>
+      <c r="M4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-    </row>
-    <row r="5" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="B5" s="5" t="s">
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+    </row>
+    <row r="5" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="6"/>
-      <c r="R5" s="6"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-    </row>
-    <row r="6" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M5" s="5"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="5"/>
+      <c r="R5" s="5"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="5"/>
+      <c r="U5" s="5"/>
+    </row>
+    <row r="6" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-    </row>
-    <row r="7" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
+      <c r="R6" s="5"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="5"/>
+      <c r="U6" s="5"/>
+    </row>
+    <row r="7" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="6"/>
-      <c r="Q7" s="6"/>
-      <c r="R7" s="6"/>
-      <c r="S7" s="6"/>
-      <c r="T7" s="6"/>
-      <c r="U7" s="6"/>
-    </row>
-    <row r="8" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M7" s="5"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
+      <c r="R7" s="5"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="5"/>
+      <c r="U7" s="5"/>
+    </row>
+    <row r="8" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
         <v>3</v>
       </c>
@@ -792,17 +892,17 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="6"/>
-      <c r="T8" s="6"/>
-      <c r="U8" s="6"/>
-    </row>
-    <row r="9" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+    </row>
+    <row r="9" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
         <v>4</v>
       </c>
@@ -812,17 +912,17 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="6"/>
-      <c r="T9" s="6"/>
-      <c r="U9" s="6"/>
-    </row>
-    <row r="10" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+      <c r="R9" s="5"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="5"/>
+      <c r="U9" s="5"/>
+    </row>
+    <row r="10" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
         <v>5</v>
       </c>
@@ -832,102 +932,102 @@
       <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="6"/>
-      <c r="T10" s="6"/>
-      <c r="U10" s="6"/>
-    </row>
-    <row r="11" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M10" s="5"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
+      <c r="R10" s="5"/>
+      <c r="S10" s="5"/>
+      <c r="T10" s="5"/>
+      <c r="U10" s="5"/>
+    </row>
+    <row r="11" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="6"/>
-      <c r="Q11" s="6"/>
-      <c r="R11" s="6"/>
-      <c r="S11" s="6"/>
-      <c r="T11" s="6"/>
-      <c r="U11" s="6"/>
-    </row>
-    <row r="12" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M11" s="5"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="5"/>
+      <c r="R11" s="5"/>
+      <c r="S11" s="5"/>
+      <c r="T11" s="5"/>
+      <c r="U11" s="5"/>
+    </row>
+    <row r="12" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
         <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6"/>
-      <c r="R12" s="6"/>
-      <c r="S12" s="6"/>
-      <c r="T12" s="6"/>
-      <c r="U12" s="6"/>
-    </row>
-    <row r="13" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="5"/>
+      <c r="R12" s="5"/>
+      <c r="S12" s="5"/>
+      <c r="T12" s="5"/>
+      <c r="U12" s="5"/>
+    </row>
+    <row r="13" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-    </row>
-    <row r="14" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="5"/>
+      <c r="R13" s="5"/>
+      <c r="S13" s="5"/>
+      <c r="T13" s="5"/>
+      <c r="U13" s="5"/>
+    </row>
+    <row r="14" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
         <v>9</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
-      <c r="S14" s="6"/>
-      <c r="T14" s="6"/>
-      <c r="U14" s="6"/>
-    </row>
-    <row r="15" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M14" s="5"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="5"/>
+      <c r="R14" s="5"/>
+      <c r="S14" s="5"/>
+      <c r="T14" s="5"/>
+      <c r="U14" s="5"/>
+    </row>
+    <row r="15" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
         <v>10</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6"/>
-      <c r="R15" s="6"/>
-      <c r="S15" s="6"/>
-      <c r="T15" s="6"/>
-      <c r="U15" s="6"/>
-    </row>
-    <row r="16" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+    </row>
+    <row r="16" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
         <v>11</v>
       </c>
@@ -937,17 +1037,17 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-      <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6"/>
-      <c r="R16" s="6"/>
-      <c r="S16" s="6"/>
-      <c r="T16" s="6"/>
-      <c r="U16" s="6"/>
-    </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M16" s="5"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
         <v>12</v>
       </c>
@@ -957,495 +1057,630 @@
       <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6"/>
-      <c r="R17" s="6"/>
-      <c r="S17" s="6"/>
-      <c r="T17" s="6"/>
-      <c r="U17" s="6"/>
-    </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
-    </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="S20" s="6"/>
-      <c r="T20" s="6"/>
-      <c r="U20" s="6"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+    </row>
+    <row r="20" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="6"/>
       <c r="G21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="4"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="6"/>
-      <c r="O21" s="6"/>
-      <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
-      <c r="R21" s="6"/>
-      <c r="S21" s="6"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="6"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="B22" s="5" t="s">
+      <c r="I21" s="6"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+    </row>
+    <row r="22" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="6"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="6"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="6"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="6"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
-      <c r="S25" s="6"/>
-      <c r="T25" s="6"/>
-      <c r="U25" s="6"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M26" s="6"/>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
-    </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-    </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-    </row>
-    <row r="29" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-    </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-    </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-    </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M33" s="6"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="6"/>
-      <c r="S33" s="6"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="6"/>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>39</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+    </row>
+    <row r="24" spans="2:21" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+    </row>
+    <row r="25" spans="2:21" ht="18" x14ac:dyDescent="0.55000000000000004">
+      <c r="B25">
+        <v>3</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B26">
+        <v>4</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="5"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B27">
+        <v>5</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B28">
+        <v>6</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+    </row>
+    <row r="29" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="5"/>
+      <c r="U29" s="5"/>
+    </row>
+    <row r="30" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B30">
+        <v>8</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="5"/>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B31">
+        <v>9</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D31" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="5"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
+      <c r="R31" s="5"/>
+      <c r="S31" s="5"/>
+      <c r="T31" s="5"/>
+      <c r="U31" s="5"/>
+    </row>
+    <row r="32" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B32">
+        <v>10</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D32" t="s">
+        <v>61</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="5"/>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B33">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+      <c r="S33" s="5"/>
+      <c r="T33" s="5"/>
+      <c r="U33" s="5"/>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="6"/>
       <c r="G34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="4"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="B35" s="5" t="s">
+      <c r="I34" s="6"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+      <c r="U34" s="5"/>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H35" s="5" t="s">
+      <c r="H35" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I35" s="5" t="s">
+      <c r="I35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="6"/>
-      <c r="S35" s="6"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="6"/>
-    </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-      <c r="U37" s="6"/>
-    </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-      <c r="U38" s="6"/>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M41" s="6"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="6"/>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M42" s="6"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M44" s="6"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-      <c r="U44" s="6"/>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M45" s="6"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-      <c r="U45" s="6"/>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.6">
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-      <c r="U47" s="6"/>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.6">
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+      <c r="U35" s="5"/>
+    </row>
+    <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37">
+        <v>2</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+      <c r="U37" s="5"/>
+    </row>
+    <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38">
+        <v>3</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+      <c r="U38" s="5"/>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40">
+        <v>5</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+      <c r="U41" s="5"/>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43">
+        <v>8</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44">
+        <v>9</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="5"/>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45">
+        <v>10</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="4"/>
+      <c r="D48" s="6"/>
       <c r="G48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.6">
-      <c r="B49" s="5" t="s">
+      <c r="I48" s="6"/>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G49" s="5" t="s">
+      <c r="G49" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H49" s="5" t="s">
+      <c r="H49" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I49" s="5" t="s">
+      <c r="I49" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="4"/>
+      <c r="D61" s="6"/>
       <c r="G61" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H61" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.6">
-      <c r="B62" s="5" t="s">
+      <c r="I61" s="6"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="5" t="s">
+      <c r="H62" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I62" s="5" t="s">
+      <c r="I62" s="4" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="M4:U47"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C34:D34"/>
     <mergeCell ref="C48:D48"/>
     <mergeCell ref="C61:D61"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="H48:I48"/>
     <mergeCell ref="H61:I61"/>
+    <mergeCell ref="M4:U47"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C34:D34"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/practice/data/theory/jungol/01_초등(미완)/정올-문제목차.xlsx
+++ b/practice/data/theory/jungol/01_초등(미완)/정올-문제목차.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\DCT2\Desktop\DCT2_공유폴더\StepCode\practice\data\theory\jungol\01_초등(미완)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DCT3\Desktop\정올-초등4+5주차\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
   <si>
     <t>정올 초등부</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -306,6 +306,70 @@
   </si>
   <si>
     <t>통로 위의 강아지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021년도 6번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년도 4번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그래프 만들기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년도 7번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>두 트리 연결하기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2019년도 10번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년도 2번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021년도 3번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2021년도 10번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년도 10번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년도 11번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022년도 12번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020년도 12번</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>블록 쌓기</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>초콜릿</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -441,17 +505,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -769,7 +833,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:U62"/>
+  <dimension ref="B2:U70"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
@@ -793,31 +857,31 @@
       <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="8"/>
       <c r="E4" t="s">
         <v>2</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="M4" s="5" t="s">
+      <c r="I4" s="8"/>
+      <c r="M4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+      <c r="R4" s="7"/>
+      <c r="S4" s="7"/>
+      <c r="T4" s="7"/>
+      <c r="U4" s="7"/>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="4" t="s">
@@ -838,15 +902,15 @@
       <c r="I5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B6">
@@ -855,15 +919,15 @@
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B7">
@@ -872,15 +936,15 @@
       <c r="C7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
     </row>
     <row r="8" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B8">
@@ -892,15 +956,15 @@
       <c r="D8" t="s">
         <v>17</v>
       </c>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B9">
@@ -912,15 +976,15 @@
       <c r="D9" t="s">
         <v>18</v>
       </c>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="5"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
     </row>
     <row r="10" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B10">
@@ -932,15 +996,15 @@
       <c r="D10" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="5"/>
-      <c r="U10" s="5"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B11">
@@ -949,15 +1013,15 @@
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="Q11" s="5"/>
-      <c r="R11" s="5"/>
-      <c r="S11" s="5"/>
-      <c r="T11" s="5"/>
-      <c r="U11" s="5"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
     </row>
     <row r="12" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B12">
@@ -966,15 +1030,15 @@
       <c r="C12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
-      <c r="U12" s="5"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
     </row>
     <row r="13" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B13">
@@ -983,15 +1047,15 @@
       <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
-      <c r="U13" s="5"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B14">
@@ -1000,15 +1064,15 @@
       <c r="C14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="5"/>
-      <c r="S14" s="5"/>
-      <c r="T14" s="5"/>
-      <c r="U14" s="5"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B15">
@@ -1017,15 +1081,15 @@
       <c r="C15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="5"/>
-      <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
-      <c r="U15" s="5"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
     </row>
     <row r="16" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B16">
@@ -1037,15 +1101,15 @@
       <c r="D16" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
-      <c r="Q16" s="5"/>
-      <c r="R16" s="5"/>
-      <c r="S16" s="5"/>
-      <c r="T16" s="5"/>
-      <c r="U16" s="5"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
     </row>
     <row r="17" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B17">
@@ -1057,73 +1121,73 @@
       <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
-      <c r="Q17" s="5"/>
-      <c r="R17" s="5"/>
-      <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
-      <c r="U17" s="5"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
-      <c r="Q18" s="5"/>
-      <c r="R18" s="5"/>
-      <c r="S18" s="5"/>
-      <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
+      <c r="U20" s="7"/>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="8"/>
       <c r="G21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="6"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
+      <c r="I21" s="8"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
+      <c r="U21" s="7"/>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="4" t="s">
@@ -1144,15 +1208,15 @@
       <c r="I22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M22" s="5"/>
-      <c r="N22" s="5"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
-      <c r="Q22" s="5"/>
-      <c r="R22" s="5"/>
-      <c r="S22" s="5"/>
-      <c r="T22" s="5"/>
-      <c r="U22" s="5"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="7"/>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B23">
@@ -1161,219 +1225,219 @@
       <c r="C23" t="s">
         <v>39</v>
       </c>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="7"/>
     </row>
     <row r="24" spans="2:21" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="B24">
         <v>2</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M24" s="5"/>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
-      <c r="Q24" s="5"/>
-      <c r="R24" s="5"/>
-      <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="7"/>
     </row>
     <row r="25" spans="2:21" ht="18" x14ac:dyDescent="0.55000000000000004">
       <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
+      <c r="U25" s="7"/>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B26">
         <v>4</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="M26" s="5"/>
-      <c r="N26" s="5"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
-      <c r="Q26" s="5"/>
-      <c r="R26" s="5"/>
-      <c r="S26" s="5"/>
-      <c r="T26" s="5"/>
-      <c r="U26" s="5"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B27">
         <v>5</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="M27" s="5"/>
-      <c r="N27" s="5"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
-      <c r="U27" s="5"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
+      <c r="U27" s="7"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B28">
         <v>6</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="5"/>
-      <c r="U28" s="5"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
+      <c r="U28" s="7"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B29">
         <v>7</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
+      <c r="U29" s="7"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B30">
         <v>8</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-      <c r="U30" s="5"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
+      <c r="U30" s="7"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B31">
         <v>9</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D31" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
+      <c r="U31" s="7"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B32">
         <v>10</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D32" t="s">
         <v>61</v>
       </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
-      <c r="Q32" s="5"/>
-      <c r="R32" s="5"/>
-      <c r="S32" s="5"/>
-      <c r="T32" s="5"/>
-      <c r="U32" s="5"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
     </row>
     <row r="33" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B33">
         <v>11</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D33" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-      <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
-      <c r="U33" s="5"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="7"/>
     </row>
     <row r="34" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D34" s="6"/>
+      <c r="D34" s="8"/>
       <c r="G34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="H34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I34" s="6"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="5"/>
-      <c r="R34" s="5"/>
-      <c r="S34" s="5"/>
-      <c r="T34" s="5"/>
-      <c r="U34" s="5"/>
+      <c r="I34" s="8"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="7"/>
     </row>
     <row r="35" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="4" t="s">
@@ -1394,223 +1458,223 @@
       <c r="I35" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="5"/>
-      <c r="N35" s="5"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
-      <c r="Q35" s="5"/>
-      <c r="R35" s="5"/>
-      <c r="S35" s="5"/>
-      <c r="T35" s="5"/>
-      <c r="U35" s="5"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
+      <c r="U35" s="7"/>
     </row>
     <row r="36" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B36">
         <v>1</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="M36" s="5"/>
-      <c r="N36" s="5"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-      <c r="S36" s="5"/>
-      <c r="T36" s="5"/>
-      <c r="U36" s="5"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+      <c r="R36" s="7"/>
+      <c r="S36" s="7"/>
+      <c r="T36" s="7"/>
+      <c r="U36" s="7"/>
     </row>
     <row r="37" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B37">
         <v>2</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-      <c r="U37" s="5"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+      <c r="R37" s="7"/>
+      <c r="S37" s="7"/>
+      <c r="T37" s="7"/>
+      <c r="U37" s="7"/>
     </row>
     <row r="38" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B38">
         <v>3</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
-      <c r="U38" s="5"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="7"/>
     </row>
     <row r="39" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B39">
         <v>4</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="M39" s="5"/>
-      <c r="N39" s="5"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-      <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
-      <c r="U39" s="5"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="7"/>
     </row>
     <row r="40" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B40">
         <v>5</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="M40" s="5"/>
-      <c r="N40" s="5"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="5"/>
-      <c r="T40" s="5"/>
-      <c r="U40" s="5"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="7"/>
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B41">
         <v>6</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="7"/>
+      <c r="Q41" s="7"/>
+      <c r="R41" s="7"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="7"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B42">
         <v>7</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M42" s="5"/>
-      <c r="N42" s="5"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+      <c r="R42" s="7"/>
+      <c r="S42" s="7"/>
+      <c r="T42" s="7"/>
+      <c r="U42" s="7"/>
     </row>
     <row r="43" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B43">
         <v>8</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="M43" s="5"/>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7"/>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+      <c r="R43" s="7"/>
+      <c r="S43" s="7"/>
+      <c r="T43" s="7"/>
+      <c r="U43" s="7"/>
     </row>
     <row r="44" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B44">
         <v>9</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
-      <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
-      <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
-      <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
-      <c r="U44" s="5"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="7"/>
+      <c r="O44" s="7"/>
+      <c r="P44" s="7"/>
+      <c r="Q44" s="7"/>
+      <c r="R44" s="7"/>
+      <c r="S44" s="7"/>
+      <c r="T44" s="7"/>
+      <c r="U44" s="7"/>
     </row>
     <row r="45" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B45">
         <v>10</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-      <c r="U45" s="5"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+      <c r="R45" s="7"/>
+      <c r="S45" s="7"/>
+      <c r="T45" s="7"/>
+      <c r="U45" s="7"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="M46" s="5"/>
-      <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="5"/>
-      <c r="S46" s="5"/>
-      <c r="T46" s="5"/>
-      <c r="U46" s="5"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+      <c r="R46" s="7"/>
+      <c r="S46" s="7"/>
+      <c r="T46" s="7"/>
+      <c r="U46" s="7"/>
     </row>
     <row r="47" spans="2:21" x14ac:dyDescent="0.55000000000000004">
-      <c r="M47" s="5"/>
-      <c r="N47" s="5"/>
-      <c r="O47" s="5"/>
-      <c r="P47" s="5"/>
-      <c r="Q47" s="5"/>
-      <c r="R47" s="5"/>
-      <c r="S47" s="5"/>
-      <c r="T47" s="5"/>
-      <c r="U47" s="5"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+      <c r="R47" s="7"/>
+      <c r="S47" s="7"/>
+      <c r="T47" s="7"/>
+      <c r="U47" s="7"/>
     </row>
     <row r="48" spans="2:21" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D48" s="6"/>
+      <c r="D48" s="8"/>
       <c r="G48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="H48" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I48" s="6"/>
+      <c r="I48" s="8"/>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="4" t="s">
@@ -1632,21 +1696,51 @@
         <v>24</v>
       </c>
     </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>64</v>
+      </c>
+      <c r="D51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52">
+        <v>3</v>
+      </c>
+      <c r="C52" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" t="s">
+        <v>67</v>
+      </c>
+    </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D61" s="6"/>
+      <c r="D61" s="8"/>
       <c r="G61" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="H61" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="I61" s="6"/>
+      <c r="I61" s="8"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="4" t="s">
@@ -1666,6 +1760,79 @@
       </c>
       <c r="I62" s="4" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64">
+        <v>2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>73</v>
+      </c>
+      <c r="D69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70">
+        <v>8</v>
+      </c>
+      <c r="C70" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
